--- a/results/reports/year_2026_report.xlsx
+++ b/results/reports/year_2026_report.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,30 +494,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return_compounded</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>top_30_excess</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>decile_return_compounded</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>decile_excess</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>OMXS30_return</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>OMXC25_return</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>OMXH25_return</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>OSEBX_return</t>
         </is>
@@ -561,21 +571,27 @@
         <v>4.16</v>
       </c>
       <c r="M2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.68</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>3.52</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>4.98</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>4.41</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>1.73</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -590,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -611,25 +627,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decile_return</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -646,18 +667,21 @@
         <v>2.32</v>
       </c>
       <c r="D2" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="E2" t="n">
         <v>1.68</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>4.98</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>4.41</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1.73</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>4.3</v>
       </c>
     </row>
@@ -964,7 +988,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7309371731304318</v>
+        <v>0.730937173130432</v>
       </c>
       <c r="E3" t="n">
         <v>0.612</v>
@@ -984,7 +1008,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.718594605488228</v>
+        <v>0.7185946054882281</v>
       </c>
       <c r="E4" t="n">
         <v>1.5834</v>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.703936312964902</v>
+        <v>0.7039363129649021</v>
       </c>
       <c r="E6" t="n">
         <v>1.2802</v>
@@ -1044,7 +1068,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.7028671117291754</v>
+        <v>0.7028671117291755</v>
       </c>
       <c r="E7" t="n">
         <v>1.05</v>
@@ -1084,7 +1108,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.7002412375442626</v>
+        <v>0.7002412375442624</v>
       </c>
       <c r="E9" t="n">
         <v>0.3436</v>
@@ -1104,7 +1128,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6978635844970362</v>
+        <v>0.6978635844970364</v>
       </c>
       <c r="E10" t="n">
         <v>7.8786</v>
@@ -1124,7 +1148,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6869062718095468</v>
+        <v>0.6869062718095467</v>
       </c>
       <c r="E11" t="n">
         <v>0.4926</v>
@@ -1144,7 +1168,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6859688815080837</v>
+        <v>0.6859688815080836</v>
       </c>
       <c r="E12" t="n">
         <v>1.7035</v>
@@ -1284,7 +1308,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6678790787321826</v>
+        <v>0.6678790787321828</v>
       </c>
       <c r="E19" t="n">
         <v>5.2471</v>
@@ -1324,7 +1348,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6663432812015533</v>
+        <v>0.6663432812015532</v>
       </c>
       <c r="E21" t="n">
         <v>0.6315</v>

--- a/results/reports/year_2026_report.xlsx
+++ b/results/reports/year_2026_report.xlsx
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7148149988284319</v>
+        <v>0.7148149988284322</v>
       </c>
       <c r="E5" t="n">
         <v>-0.4201</v>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7039363129649021</v>
+        <v>0.703936312964902</v>
       </c>
       <c r="E6" t="n">
         <v>1.2802</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.7026089722159558</v>
+        <v>0.7026089722159559</v>
       </c>
       <c r="E8" t="n">
         <v>5.3471</v>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6978635844970364</v>
+        <v>0.6978635844970362</v>
       </c>
       <c r="E10" t="n">
         <v>7.8786</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6869062718095467</v>
+        <v>0.6869062718095468</v>
       </c>
       <c r="E11" t="n">
         <v>0.4926</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6859688815080836</v>
+        <v>0.6859688815080834</v>
       </c>
       <c r="E12" t="n">
         <v>1.7035</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6774232143711505</v>
+        <v>0.6774232143711504</v>
       </c>
       <c r="E15" t="n">
         <v>1.9136</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6728402189993489</v>
+        <v>0.6728402189993491</v>
       </c>
       <c r="E16" t="n">
         <v>-3.125</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6678790787321828</v>
+        <v>0.6678790787321826</v>
       </c>
       <c r="E19" t="n">
         <v>5.2471</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6663432812015532</v>
+        <v>0.6663432812015533</v>
       </c>
       <c r="E21" t="n">
         <v>0.6315</v>

--- a/results/reports/year_2026_report.xlsx
+++ b/results/reports/year_2026_report.xlsx
@@ -1028,7 +1028,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7148149988284322</v>
+        <v>0.7148149988284319</v>
       </c>
       <c r="E5" t="n">
         <v>-0.4201</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.7028671117291755</v>
+        <v>0.7028671117291754</v>
       </c>
       <c r="E7" t="n">
         <v>1.05</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6859688815080834</v>
+        <v>0.6859688815080836</v>
       </c>
       <c r="E12" t="n">
         <v>1.7035</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6691110522613656</v>
+        <v>0.6691110522613655</v>
       </c>
       <c r="E17" t="n">
         <v>3.174</v>

--- a/results/reports/year_2026_report.xlsx
+++ b/results/reports/year_2026_report.xlsx
@@ -1048,7 +1048,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.703936312964902</v>
+        <v>0.7039363129649021</v>
       </c>
       <c r="E6" t="n">
         <v>1.2802</v>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.7028671117291754</v>
+        <v>0.7028671117291755</v>
       </c>
       <c r="E7" t="n">
         <v>1.05</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.7026089722159559</v>
+        <v>0.7026089722159558</v>
       </c>
       <c r="E8" t="n">
         <v>5.3471</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6869062718095468</v>
+        <v>0.6869062718095467</v>
       </c>
       <c r="E11" t="n">
         <v>0.4926</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6774232143711504</v>
+        <v>0.6774232143711505</v>
       </c>
       <c r="E15" t="n">
         <v>1.9136</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6728402189993491</v>
+        <v>0.6728402189993489</v>
       </c>
       <c r="E16" t="n">
         <v>-3.125</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6691110522613655</v>
+        <v>0.6691110522613656</v>
       </c>
       <c r="E17" t="n">
         <v>3.174</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6663432812015533</v>
+        <v>0.6663432812015532</v>
       </c>
       <c r="E21" t="n">
         <v>0.6315</v>
